--- a/project/Villafuerte_Roberto/peer_evaluation_villafuerte_roberto.xlsx
+++ b/project/Villafuerte_Roberto/peer_evaluation_villafuerte_roberto.xlsx
@@ -44,7 +44,7 @@
     <t>Andrés Proaño</t>
   </si>
   <si>
-    <t>Roberto Villafuertes</t>
+    <t>Pablo Alvarado</t>
   </si>
   <si>
     <t>Leyó los capítulos asignados y aportó ideas únicas</t>
